--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/18.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/18.xlsx
@@ -426,13 +426,13 @@
         <v>-14.18157504004578</v>
       </c>
       <c r="E2">
-        <v>-13.62395207203961</v>
+        <v>-9.624737669924381</v>
       </c>
       <c r="F2">
-        <v>4.678853371739092</v>
+        <v>5.671433014999961</v>
       </c>
       <c r="G2">
-        <v>-17.79220948517271</v>
+        <v>-17.63366940913276</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-13.96975964410889</v>
       </c>
       <c r="E3">
-        <v>-13.00893623263634</v>
+        <v>-9.829337319419409</v>
       </c>
       <c r="F3">
-        <v>4.783759476364427</v>
+        <v>5.573932514955653</v>
       </c>
       <c r="G3">
-        <v>-17.7082805734299</v>
+        <v>-16.44067661450059</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-13.71072669345534</v>
       </c>
       <c r="E4">
-        <v>-14.7091363526814</v>
+        <v>-10.05015525913789</v>
       </c>
       <c r="F4">
-        <v>4.412442131324743</v>
+        <v>5.396854071994008</v>
       </c>
       <c r="G4">
-        <v>-16.76853522562489</v>
+        <v>-15.68830440599979</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-13.4175202652338</v>
       </c>
       <c r="E5">
-        <v>-14.84204326828724</v>
+        <v>-10.99551752731801</v>
       </c>
       <c r="F5">
-        <v>5.463734799361235</v>
+        <v>6.008505651607913</v>
       </c>
       <c r="G5">
-        <v>-15.86058613619506</v>
+        <v>-15.67615922216193</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-13.10606193931164</v>
       </c>
       <c r="E6">
-        <v>-16.3577369752268</v>
+        <v>-11.52926332751703</v>
       </c>
       <c r="F6">
-        <v>5.018883279975038</v>
+        <v>6.169681097170613</v>
       </c>
       <c r="G6">
-        <v>-16.00933200390145</v>
+        <v>-14.50274440121852</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-12.79842938937143</v>
       </c>
       <c r="E7">
-        <v>-16.45478091104274</v>
+        <v>-12.67848182036504</v>
       </c>
       <c r="F7">
-        <v>4.501620852440527</v>
+        <v>6.197114968816527</v>
       </c>
       <c r="G7">
-        <v>-15.23216685939114</v>
+        <v>-13.85540897447969</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-12.49263286877453</v>
       </c>
       <c r="E8">
-        <v>-16.07488251794935</v>
+        <v>-13.26312937856115</v>
       </c>
       <c r="F8">
-        <v>5.207911751089469</v>
+        <v>6.454970830694762</v>
       </c>
       <c r="G8">
-        <v>-14.18548280238955</v>
+        <v>-12.88452658130877</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-12.2135584501334</v>
       </c>
       <c r="E9">
-        <v>-16.92469600639047</v>
+        <v>-14.23998129500612</v>
       </c>
       <c r="F9">
-        <v>5.688232305928735</v>
+        <v>6.45384259429215</v>
       </c>
       <c r="G9">
-        <v>-14.85180878528414</v>
+        <v>-13.16358645990828</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-11.95342395413811</v>
       </c>
       <c r="E10">
-        <v>-17.65354721499595</v>
+        <v>-14.32365189035612</v>
       </c>
       <c r="F10">
-        <v>5.732274944000778</v>
+        <v>6.639408489662878</v>
       </c>
       <c r="G10">
-        <v>-14.17677988529507</v>
+        <v>-12.52846670711126</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-11.72766239265503</v>
       </c>
       <c r="E11">
-        <v>-17.9738221063101</v>
+        <v>-14.94360174481328</v>
       </c>
       <c r="F11">
-        <v>5.431681951077311</v>
+        <v>7.141947514980032</v>
       </c>
       <c r="G11">
-        <v>-13.97398768843576</v>
+        <v>-11.96210874535499</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-11.53938967467531</v>
       </c>
       <c r="E12">
-        <v>-19.62383066749461</v>
+        <v>-15.36424314100323</v>
       </c>
       <c r="F12">
-        <v>6.405446057150991</v>
+        <v>7.35546086978641</v>
       </c>
       <c r="G12">
-        <v>-12.66054166523109</v>
+        <v>-11.58579863073651</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-11.38212263053481</v>
       </c>
       <c r="E13">
-        <v>-21.26943267146347</v>
+        <v>-16.80087216395203</v>
       </c>
       <c r="F13">
-        <v>6.952440247506783</v>
+        <v>7.433937084058024</v>
       </c>
       <c r="G13">
-        <v>-12.45374980765819</v>
+        <v>-11.28010915730765</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-11.26664206710737</v>
       </c>
       <c r="E14">
-        <v>-19.84415022185411</v>
+        <v>-17.18622787672624</v>
       </c>
       <c r="F14">
-        <v>6.234613504406455</v>
+        <v>7.680228936993179</v>
       </c>
       <c r="G14">
-        <v>-12.57657228694712</v>
+        <v>-10.81765883027768</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-11.16967188634091</v>
       </c>
       <c r="E15">
-        <v>-20.87673823427829</v>
+        <v>-18.78660971579037</v>
       </c>
       <c r="F15">
-        <v>6.506821659905595</v>
+        <v>7.963288705468992</v>
       </c>
       <c r="G15">
-        <v>-12.10613830295753</v>
+        <v>-10.82375883501482</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-11.08927621663119</v>
       </c>
       <c r="E16">
-        <v>-23.46560928791956</v>
+        <v>-18.55550427162029</v>
       </c>
       <c r="F16">
-        <v>6.737793686093376</v>
+        <v>8.192436666635809</v>
       </c>
       <c r="G16">
-        <v>-11.74508407435722</v>
+        <v>-10.07534451531415</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-11.00101258269436</v>
       </c>
       <c r="E17">
-        <v>-22.08869513739915</v>
+        <v>-19.66324048975591</v>
       </c>
       <c r="F17">
-        <v>7.467986297782695</v>
+        <v>8.681494840839802</v>
       </c>
       <c r="G17">
-        <v>-11.57996622731996</v>
+        <v>-10.29078446434511</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-10.89046821779485</v>
       </c>
       <c r="E18">
-        <v>-23.3415985509715</v>
+        <v>-21.26110132954587</v>
       </c>
       <c r="F18">
-        <v>7.315003405833682</v>
+        <v>8.812931896642</v>
       </c>
       <c r="G18">
-        <v>-10.58331970115165</v>
+        <v>-9.316673885487287</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-10.75037061679936</v>
       </c>
       <c r="E19">
-        <v>-24.78491424415327</v>
+        <v>-22.27298143030444</v>
       </c>
       <c r="F19">
-        <v>7.499152792945623</v>
+        <v>8.864905324228447</v>
       </c>
       <c r="G19">
-        <v>-10.78311215247578</v>
+        <v>-8.950232385423217</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-10.56132201560796</v>
       </c>
       <c r="E20">
-        <v>-25.59175445501639</v>
+        <v>-22.69578249638332</v>
       </c>
       <c r="F20">
-        <v>8.04616023717986</v>
+        <v>9.119547120583821</v>
       </c>
       <c r="G20">
-        <v>-10.43915569020267</v>
+        <v>-9.096654690443509</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-10.33189465463358</v>
       </c>
       <c r="E21">
-        <v>-25.3255045366156</v>
+        <v>-23.08439017362487</v>
       </c>
       <c r="F21">
-        <v>8.003381687764488</v>
+        <v>9.107837318977847</v>
       </c>
       <c r="G21">
-        <v>-10.80892066813123</v>
+        <v>-8.404672920452047</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-10.05445233034015</v>
       </c>
       <c r="E22">
-        <v>-24.54950607305066</v>
+        <v>-22.93357045757505</v>
       </c>
       <c r="F22">
-        <v>8.136160698759221</v>
+        <v>9.221108277636651</v>
       </c>
       <c r="G22">
-        <v>-10.01030172994345</v>
+        <v>-8.161932415231812</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-9.742866550475744</v>
       </c>
       <c r="E23">
-        <v>-26.66653494128949</v>
+        <v>-23.75842729916527</v>
       </c>
       <c r="F23">
-        <v>8.766788518836456</v>
+        <v>9.182264473384576</v>
       </c>
       <c r="G23">
-        <v>-9.549477896793745</v>
+        <v>-7.645051979594021</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-9.408634548238856</v>
       </c>
       <c r="E24">
-        <v>-27.09549937297441</v>
+        <v>-24.77280763314139</v>
       </c>
       <c r="F24">
-        <v>8.283808904634204</v>
+        <v>9.356145418171415</v>
       </c>
       <c r="G24">
-        <v>-9.037514798593316</v>
+        <v>-7.093289385474366</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-9.057224372719247</v>
       </c>
       <c r="E25">
-        <v>-28.29563000684782</v>
+        <v>-25.69627417121702</v>
       </c>
       <c r="F25">
-        <v>7.810907208254411</v>
+        <v>9.029713989219825</v>
       </c>
       <c r="G25">
-        <v>-9.45715283044591</v>
+        <v>-7.064881873578463</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-8.712725155846684</v>
       </c>
       <c r="E26">
-        <v>-26.36746634699991</v>
+        <v>-25.58088134776798</v>
       </c>
       <c r="F26">
-        <v>8.983467893856334</v>
+        <v>9.095453226305994</v>
       </c>
       <c r="G26">
-        <v>-9.746720956024649</v>
+        <v>-6.843728310009847</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-8.376220558791344</v>
       </c>
       <c r="E27">
-        <v>-25.57702716765854</v>
+        <v>-25.81659685650863</v>
       </c>
       <c r="F27">
-        <v>8.07748412214932</v>
+        <v>9.421813415660942</v>
       </c>
       <c r="G27">
-        <v>-9.513377825960125</v>
+        <v>-6.456332973857502</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-8.067474029791224</v>
       </c>
       <c r="E28">
-        <v>-27.89213514361242</v>
+        <v>-26.42145809422268</v>
       </c>
       <c r="F28">
-        <v>7.596197690918391</v>
+        <v>9.183409277135246</v>
       </c>
       <c r="G28">
-        <v>-8.599435772321394</v>
+        <v>-6.194417854987835</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-7.789319704507066</v>
       </c>
       <c r="E29">
-        <v>-27.85547890045948</v>
+        <v>-26.54312226677221</v>
       </c>
       <c r="F29">
-        <v>8.079391023910565</v>
+        <v>9.004745338964643</v>
       </c>
       <c r="G29">
-        <v>-7.981699662384306</v>
+        <v>-6.230370418752056</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-7.548784125532822</v>
       </c>
       <c r="E30">
-        <v>-28.33020756773268</v>
+        <v>-26.40420980759067</v>
       </c>
       <c r="F30">
-        <v>7.787138033998483</v>
+        <v>8.775405196560376</v>
       </c>
       <c r="G30">
-        <v>-8.40222795814247</v>
+        <v>-6.341750004498131</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-7.356218763650257</v>
       </c>
       <c r="E31">
-        <v>-27.67089772955013</v>
+        <v>-27.72270904082736</v>
       </c>
       <c r="F31">
-        <v>8.273467565977656</v>
+        <v>8.614243004876123</v>
       </c>
       <c r="G31">
-        <v>-8.393090352073573</v>
+        <v>-5.754943385731962</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-7.205212063441479</v>
       </c>
       <c r="E32">
-        <v>-27.93089706490704</v>
+        <v>-26.59942319949159</v>
       </c>
       <c r="F32">
-        <v>7.759836701137017</v>
+        <v>8.628878600148784</v>
       </c>
       <c r="G32">
-        <v>-8.256947853880789</v>
+        <v>-5.674122565424868</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-7.108388769182018</v>
       </c>
       <c r="E33">
-        <v>-27.51219521840578</v>
+        <v>-28.05221236770528</v>
       </c>
       <c r="F33">
-        <v>8.446266662936438</v>
+        <v>8.656507966501758</v>
       </c>
       <c r="G33">
-        <v>-7.624818709012893</v>
+        <v>-6.472822436694973</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-7.056746466728026</v>
       </c>
       <c r="E34">
-        <v>-28.56308850974413</v>
+        <v>-27.14554556943859</v>
       </c>
       <c r="F34">
-        <v>7.453435195985119</v>
+        <v>8.639909140484463</v>
       </c>
       <c r="G34">
-        <v>-8.114894629933724</v>
+        <v>-5.7195025279076</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-7.056710528002887</v>
       </c>
       <c r="E35">
-        <v>-27.66296094270838</v>
+        <v>-26.9630160849237</v>
       </c>
       <c r="F35">
-        <v>7.446571343685522</v>
+        <v>9.002319879209246</v>
       </c>
       <c r="G35">
-        <v>-8.089489474317601</v>
+        <v>-5.72621214150676</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-7.106190871762769</v>
       </c>
       <c r="E36">
-        <v>-28.16848982516651</v>
+        <v>-26.39462834906429</v>
       </c>
       <c r="F36">
-        <v>7.587151918879821</v>
+        <v>8.79584102038744</v>
       </c>
       <c r="G36">
-        <v>-8.135009111635956</v>
+        <v>-5.560821471659734</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-7.196959140715563</v>
       </c>
       <c r="E37">
-        <v>-26.49145216468002</v>
+        <v>-26.10187263598845</v>
       </c>
       <c r="F37">
-        <v>7.499926488099838</v>
+        <v>8.692237109319306</v>
       </c>
       <c r="G37">
-        <v>-9.202040006608389</v>
+        <v>-6.03315738308395</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-7.334211166040891</v>
       </c>
       <c r="E38">
-        <v>-27.51068760269487</v>
+        <v>-26.78088530869599</v>
       </c>
       <c r="F38">
-        <v>7.73975210508874</v>
+        <v>8.825995250584148</v>
       </c>
       <c r="G38">
-        <v>-8.420967882817481</v>
+        <v>-6.218883142551157</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-7.501817104559151</v>
       </c>
       <c r="E39">
-        <v>-27.34378249918398</v>
+        <v>-26.82575660384944</v>
       </c>
       <c r="F39">
-        <v>8.330275345726839</v>
+        <v>9.07854459088005</v>
       </c>
       <c r="G39">
-        <v>-7.930012140969445</v>
+        <v>-5.751956693919729</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-7.702153520991865</v>
       </c>
       <c r="E40">
-        <v>-27.15123131574228</v>
+        <v>-25.7598515301775</v>
       </c>
       <c r="F40">
-        <v>7.8542821821998</v>
+        <v>9.012336497843897</v>
       </c>
       <c r="G40">
-        <v>-8.652919486014941</v>
+        <v>-5.891341736894676</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-7.920076310715306</v>
       </c>
       <c r="E41">
-        <v>-26.01198883649651</v>
+        <v>-25.14108534094791</v>
       </c>
       <c r="F41">
-        <v>7.677581474773831</v>
+        <v>9.233346577645611</v>
       </c>
       <c r="G41">
-        <v>-9.282657188837376</v>
+        <v>-5.985785422478199</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-8.149094323451216</v>
       </c>
       <c r="E42">
-        <v>-24.92284654546215</v>
+        <v>-25.26172367030021</v>
       </c>
       <c r="F42">
-        <v>8.526636525090852</v>
+        <v>9.631512966944832</v>
       </c>
       <c r="G42">
-        <v>-8.147722132422382</v>
+        <v>-6.253078675205559</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-8.385011476304632</v>
       </c>
       <c r="E43">
-        <v>-26.89408938977684</v>
+        <v>-25.49966114709964</v>
       </c>
       <c r="F43">
-        <v>7.69196193288643</v>
+        <v>9.681899242587516</v>
       </c>
       <c r="G43">
-        <v>-8.759239448743438</v>
+        <v>-6.354657525756595</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-8.61290014515501</v>
       </c>
       <c r="E44">
-        <v>-24.16295008220357</v>
+        <v>-25.33607030622596</v>
       </c>
       <c r="F44">
-        <v>9.037835303236871</v>
+        <v>9.569352277038757</v>
       </c>
       <c r="G44">
-        <v>-8.368072892029231</v>
+        <v>-6.919118781567425</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-8.836604993017875</v>
       </c>
       <c r="E45">
-        <v>-25.23322018097791</v>
+        <v>-23.57679075508522</v>
       </c>
       <c r="F45">
-        <v>8.040376575973514</v>
+        <v>9.633979845070369</v>
       </c>
       <c r="G45">
-        <v>-9.3842686736958</v>
+        <v>-7.034962740564304</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-9.040898749170035</v>
       </c>
       <c r="E46">
-        <v>-26.27785250624408</v>
+        <v>-23.79746333240733</v>
       </c>
       <c r="F46">
-        <v>8.736438793932688</v>
+        <v>9.619675596758828</v>
       </c>
       <c r="G46">
-        <v>-9.760283774175482</v>
+        <v>-6.783404445487584</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-9.229549594687072</v>
       </c>
       <c r="E47">
-        <v>-25.25617497997024</v>
+        <v>-23.4452253267373</v>
       </c>
       <c r="F47">
-        <v>8.845453600875908</v>
+        <v>10.12558773414018</v>
       </c>
       <c r="G47">
-        <v>-10.13415545334586</v>
+        <v>-7.018157377631308</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-9.398813573446086</v>
       </c>
       <c r="E48">
-        <v>-24.58124906720633</v>
+        <v>-23.11841328079787</v>
       </c>
       <c r="F48">
-        <v>7.976989902311296</v>
+        <v>9.706369215666212</v>
       </c>
       <c r="G48">
-        <v>-9.851607619972626</v>
+        <v>-7.404735550726635</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-9.543118784880409</v>
       </c>
       <c r="E49">
-        <v>-23.39994286366269</v>
+        <v>-22.16124343282126</v>
       </c>
       <c r="F49">
-        <v>7.450481237826736</v>
+        <v>9.927677507732934</v>
       </c>
       <c r="G49">
-        <v>-9.65283988590051</v>
+        <v>-6.793706443644116</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-9.671320080136566</v>
       </c>
       <c r="E50">
-        <v>-23.66492189939808</v>
+        <v>-22.38343193227693</v>
       </c>
       <c r="F50">
-        <v>7.891142874889572</v>
+        <v>9.923384907851627</v>
       </c>
       <c r="G50">
-        <v>-10.33084634009574</v>
+        <v>-7.282291629403421</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-9.773686106603346</v>
       </c>
       <c r="E51">
-        <v>-23.11956787354617</v>
+        <v>-22.26575899581057</v>
       </c>
       <c r="F51">
-        <v>8.594536144363522</v>
+        <v>9.850067765764649</v>
       </c>
       <c r="G51">
-        <v>-9.624373632251308</v>
+        <v>-7.173760366006251</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-9.860761413632144</v>
       </c>
       <c r="E52">
-        <v>-22.14322680209415</v>
+        <v>-21.84724404381892</v>
       </c>
       <c r="F52">
-        <v>8.633802415991024</v>
+        <v>9.80223948866181</v>
       </c>
       <c r="G52">
-        <v>-9.975450900396675</v>
+        <v>-8.291955328103027</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-9.92707888736725</v>
       </c>
       <c r="E53">
-        <v>-23.17121720958174</v>
+        <v>-21.23849955351615</v>
       </c>
       <c r="F53">
-        <v>7.93597080525947</v>
+        <v>9.602104267410644</v>
       </c>
       <c r="G53">
-        <v>-10.95023505135901</v>
+        <v>-8.265513706884231</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-9.975485144978613</v>
       </c>
       <c r="E54">
-        <v>-22.0064366338996</v>
+        <v>-20.2599946589639</v>
       </c>
       <c r="F54">
-        <v>8.348501085323235</v>
+        <v>9.985512463061589</v>
       </c>
       <c r="G54">
-        <v>-9.978432370719727</v>
+        <v>-7.879577776958318</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-10.01423941635639</v>
       </c>
       <c r="E55">
-        <v>-21.96296081775129</v>
+        <v>-20.51361466172588</v>
       </c>
       <c r="F55">
-        <v>8.531351592347587</v>
+        <v>9.69664252562254</v>
       </c>
       <c r="G55">
-        <v>-9.90984549956659</v>
+        <v>-7.822809746569152</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-10.03754915653787</v>
       </c>
       <c r="E56">
-        <v>-20.32258355362906</v>
+        <v>-19.69407808384276</v>
       </c>
       <c r="F56">
-        <v>8.470353930275042</v>
+        <v>9.637114387322562</v>
       </c>
       <c r="G56">
-        <v>-10.72703858014785</v>
+        <v>-7.679289284161881</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-10.06075359792353</v>
       </c>
       <c r="E57">
-        <v>-21.82060949959279</v>
+        <v>-20.1108860659799</v>
       </c>
       <c r="F57">
-        <v>8.278378127941451</v>
+        <v>9.820962248699885</v>
       </c>
       <c r="G57">
-        <v>-10.14209342227514</v>
+        <v>-8.48411918373192</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-10.07679199845457</v>
       </c>
       <c r="E58">
-        <v>-20.08536042917751</v>
+        <v>-19.50334185375001</v>
       </c>
       <c r="F58">
-        <v>8.696072450394269</v>
+        <v>9.716341102461113</v>
       </c>
       <c r="G58">
-        <v>-11.64508472428381</v>
+        <v>-8.541894961533258</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-10.0965931807468</v>
       </c>
       <c r="E59">
-        <v>-20.15443663993205</v>
+        <v>-19.16517908125982</v>
       </c>
       <c r="F59">
-        <v>7.970367933293317</v>
+        <v>9.90793419905461</v>
       </c>
       <c r="G59">
-        <v>-11.07710940625334</v>
+        <v>-8.636252492545273</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-10.12328243801726</v>
       </c>
       <c r="E60">
-        <v>-20.43461227590499</v>
+        <v>-18.5559237459641</v>
       </c>
       <c r="F60">
-        <v>8.163226775278291</v>
+        <v>9.881260768684466</v>
       </c>
       <c r="G60">
-        <v>-11.1118179502199</v>
+        <v>-8.829206098412978</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-10.15244270057846</v>
       </c>
       <c r="E61">
-        <v>-20.57943475480176</v>
+        <v>-17.59511983807826</v>
       </c>
       <c r="F61">
-        <v>8.691595952949539</v>
+        <v>9.863575124634696</v>
       </c>
       <c r="G61">
-        <v>-10.18927088240885</v>
+        <v>-8.471323924490873</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-10.19673563347659</v>
       </c>
       <c r="E62">
-        <v>-19.76820875277962</v>
+        <v>-18.06312860942789</v>
       </c>
       <c r="F62">
-        <v>8.31211587552267</v>
+        <v>9.578383138464078</v>
       </c>
       <c r="G62">
-        <v>-11.40263923320237</v>
+        <v>-8.567119975772593</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-10.24455743538022</v>
       </c>
       <c r="E63">
-        <v>-19.63116939190558</v>
+        <v>-17.70183244985841</v>
       </c>
       <c r="F63">
-        <v>7.831965964368381</v>
+        <v>9.909188347302448</v>
       </c>
       <c r="G63">
-        <v>-11.46611165570151</v>
+        <v>-8.428405894157562</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-10.3059851470728</v>
       </c>
       <c r="E64">
-        <v>-19.69127881940982</v>
+        <v>-17.40872371381996</v>
       </c>
       <c r="F64">
-        <v>8.099271841577753</v>
+        <v>9.705009036390816</v>
       </c>
       <c r="G64">
-        <v>-10.41173373438991</v>
+        <v>-8.747201305433814</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-10.37340951450457</v>
       </c>
       <c r="E65">
-        <v>-17.24421086003217</v>
+        <v>-18.04729656785764</v>
       </c>
       <c r="F65">
-        <v>8.188793506798296</v>
+        <v>9.992797126001809</v>
       </c>
       <c r="G65">
-        <v>-11.66300618052951</v>
+        <v>-8.377198749747466</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-10.44415363864945</v>
       </c>
       <c r="E66">
-        <v>-18.65966265843566</v>
+        <v>-16.93843898266432</v>
       </c>
       <c r="F66">
-        <v>7.801727240696588</v>
+        <v>9.695734634949073</v>
       </c>
       <c r="G66">
-        <v>-11.54107004902926</v>
+        <v>-9.00374090119038</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-10.52305183270223</v>
       </c>
       <c r="E67">
-        <v>-19.63048411203699</v>
+        <v>-17.6825781621565</v>
       </c>
       <c r="F67">
-        <v>8.131894606634804</v>
+        <v>9.862730189883841</v>
       </c>
       <c r="G67">
-        <v>-10.84299480116214</v>
+        <v>-8.643716611331266</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-10.5962656074007</v>
       </c>
       <c r="E68">
-        <v>-18.40457657207602</v>
+        <v>-17.51583918709861</v>
       </c>
       <c r="F68">
-        <v>8.185852802518358</v>
+        <v>9.491484084440799</v>
       </c>
       <c r="G68">
-        <v>-11.85502644520589</v>
+        <v>-8.294453810676721</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-10.67273516796278</v>
       </c>
       <c r="E69">
-        <v>-18.03912304797038</v>
+        <v>-17.22381859242726</v>
       </c>
       <c r="F69">
-        <v>7.834623366996562</v>
+        <v>10.07787542847374</v>
       </c>
       <c r="G69">
-        <v>-11.68375898928426</v>
+        <v>-8.576749707196916</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-10.73740834240204</v>
       </c>
       <c r="E70">
-        <v>-18.71171070275842</v>
+        <v>-15.89128565812398</v>
       </c>
       <c r="F70">
-        <v>7.958225723903081</v>
+        <v>10.00526074194433</v>
       </c>
       <c r="G70">
-        <v>-11.42409824836902</v>
+        <v>-8.389820394473203</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-10.79386758890312</v>
       </c>
       <c r="E71">
-        <v>-18.35076341294022</v>
+        <v>-17.24989660633586</v>
       </c>
       <c r="F71">
-        <v>8.170297719428589</v>
+        <v>9.801116222463614</v>
       </c>
       <c r="G71">
-        <v>-10.60063415927991</v>
+        <v>-9.040395755249611</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-10.84041545071864</v>
       </c>
       <c r="E72">
-        <v>-18.35095861387248</v>
+        <v>-15.9717832000218</v>
       </c>
       <c r="F72">
-        <v>8.232069076655348</v>
+        <v>9.74140584333502</v>
       </c>
       <c r="G72">
-        <v>-10.61252871163703</v>
+        <v>-8.68806141358362</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-10.86782883679028</v>
       </c>
       <c r="E73">
-        <v>-18.06502662700334</v>
+        <v>-16.49067711652323</v>
       </c>
       <c r="F73">
-        <v>7.87515207054593</v>
+        <v>9.599027710876648</v>
       </c>
       <c r="G73">
-        <v>-10.14170572670336</v>
+        <v>-8.405884305942324</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-10.88721930248413</v>
       </c>
       <c r="E74">
-        <v>-19.07112961080908</v>
+        <v>-16.26947708136287</v>
       </c>
       <c r="F74">
-        <v>7.899842389353772</v>
+        <v>9.438365853103683</v>
       </c>
       <c r="G74">
-        <v>-11.02459036268621</v>
+        <v>-8.555885941797033</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-10.88687953501869</v>
       </c>
       <c r="E75">
-        <v>-19.28685986665464</v>
+        <v>-16.31773324374605</v>
       </c>
       <c r="F75">
-        <v>7.503896024694053</v>
+        <v>9.818024857889558</v>
       </c>
       <c r="G75">
-        <v>-10.51908755197649</v>
+        <v>-8.7449730349253</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-10.87723112710838</v>
       </c>
       <c r="E76">
-        <v>-18.73300006400949</v>
+        <v>-17.02639569210154</v>
       </c>
       <c r="F76">
-        <v>7.775678399348155</v>
+        <v>9.689177278588511</v>
       </c>
       <c r="G76">
-        <v>-11.25331508556905</v>
+        <v>-8.334064027613092</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-10.85419970752767</v>
       </c>
       <c r="E77">
-        <v>-19.71930468942977</v>
+        <v>-17.41709658785081</v>
       </c>
       <c r="F77">
-        <v>7.61888667408107</v>
+        <v>9.737963148408985</v>
       </c>
       <c r="G77">
-        <v>-10.36470900281478</v>
+        <v>-7.925318022194624</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-10.81530793574087</v>
       </c>
       <c r="E78">
-        <v>-19.38700625133024</v>
+        <v>-17.65124218271067</v>
       </c>
       <c r="F78">
-        <v>7.421885995082096</v>
+        <v>9.69026243988618</v>
       </c>
       <c r="G78">
-        <v>-9.559975700794611</v>
+        <v>-7.575825476016061</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-10.7678822161612</v>
       </c>
       <c r="E79">
-        <v>-20.83242346944236</v>
+        <v>-17.44192448515064</v>
       </c>
       <c r="F79">
-        <v>7.301852244946837</v>
+        <v>9.675408155619179</v>
       </c>
       <c r="G79">
-        <v>-9.727969282998979</v>
+        <v>-7.934180194709158</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-10.69889143054735</v>
       </c>
       <c r="E80">
-        <v>-19.93763485556468</v>
+        <v>-17.80409281909834</v>
       </c>
       <c r="F80">
-        <v>8.185958833545916</v>
+        <v>9.783008111038416</v>
       </c>
       <c r="G80">
-        <v>-9.905244062224753</v>
+        <v>-7.306018076247459</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-10.61664771937269</v>
       </c>
       <c r="E81">
-        <v>-19.7870560257717</v>
+        <v>-18.95081107872879</v>
       </c>
       <c r="F81">
-        <v>7.627480157517712</v>
+        <v>9.547031089002923</v>
       </c>
       <c r="G81">
-        <v>-9.870231366513332</v>
+        <v>-7.286273014904869</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-10.50870378289952</v>
       </c>
       <c r="E82">
-        <v>-21.21593100317703</v>
+        <v>-18.88471687370547</v>
       </c>
       <c r="F82">
-        <v>8.126521815660245</v>
+        <v>9.786465716577702</v>
       </c>
       <c r="G82">
-        <v>-9.818643053392934</v>
+        <v>-7.109812787991522</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-10.37567322361522</v>
       </c>
       <c r="E83">
-        <v>-22.05102135747163</v>
+        <v>-19.69514130594192</v>
       </c>
       <c r="F83">
-        <v>7.512451403230167</v>
+        <v>9.608804102964486</v>
       </c>
       <c r="G83">
-        <v>-8.898449571830781</v>
+        <v>-6.812866698198297</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-10.21713776337826</v>
       </c>
       <c r="E84">
-        <v>-24.12770177768975</v>
+        <v>-21.29605475605563</v>
       </c>
       <c r="F84">
-        <v>7.891190920198934</v>
+        <v>9.397618460559976</v>
       </c>
       <c r="G84">
-        <v>-7.84506112271921</v>
+        <v>-6.203328326277305</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-10.02171688458024</v>
       </c>
       <c r="E85">
-        <v>-23.03646626814767</v>
+        <v>-21.51673148658907</v>
       </c>
       <c r="F85">
-        <v>8.062952901169412</v>
+        <v>9.655119781189812</v>
       </c>
       <c r="G85">
-        <v>-9.61681944277692</v>
+        <v>-6.344955998856018</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-9.797745550013397</v>
       </c>
       <c r="E86">
-        <v>-24.4382581545038</v>
+        <v>-23.18071975709294</v>
       </c>
       <c r="F86">
-        <v>7.729183793763823</v>
+        <v>9.783611162507656</v>
       </c>
       <c r="G86">
-        <v>-8.794780820234559</v>
+        <v>-6.548335613248335</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-9.534294895869245</v>
       </c>
       <c r="E87">
-        <v>-25.43451387425837</v>
+        <v>-23.56463430553745</v>
       </c>
       <c r="F87">
-        <v>7.652281477557529</v>
+        <v>9.714798682357101</v>
       </c>
       <c r="G87">
-        <v>-9.769370470724853</v>
+        <v>-6.636114067890745</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-9.236698596847035</v>
       </c>
       <c r="E88">
-        <v>-27.48297737673561</v>
+        <v>-25.71245508253855</v>
       </c>
       <c r="F88">
-        <v>7.550084134339349</v>
+        <v>9.988244418756024</v>
       </c>
       <c r="G88">
-        <v>-8.14601601083209</v>
+        <v>-6.467128402741755</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-8.90413879617638</v>
       </c>
       <c r="E89">
-        <v>-28.32904466856173</v>
+        <v>-26.46379593046798</v>
       </c>
       <c r="F89">
-        <v>8.108475003422855</v>
+        <v>9.82966010642928</v>
       </c>
       <c r="G89">
-        <v>-7.999608064907047</v>
+        <v>-6.034718608349436</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-8.532144536283743</v>
       </c>
       <c r="E90">
-        <v>-32.29242931657766</v>
+        <v>-28.22161770443372</v>
       </c>
       <c r="F90">
-        <v>7.954463279159566</v>
+        <v>10.02625322866608</v>
       </c>
       <c r="G90">
-        <v>-7.854924515784436</v>
+        <v>-5.186573845268235</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-8.13140109274873</v>
       </c>
       <c r="E91">
-        <v>-31.70467307970491</v>
+        <v>-29.74667897951642</v>
       </c>
       <c r="F91">
-        <v>8.042131058132643</v>
+        <v>10.06361259853233</v>
       </c>
       <c r="G91">
-        <v>-7.958381797068777</v>
+        <v>-5.470507984019352</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-7.695766116830392</v>
       </c>
       <c r="E92">
-        <v>-33.84286671285506</v>
+        <v>-30.50325287371513</v>
       </c>
       <c r="F92">
-        <v>7.305417538248486</v>
+        <v>9.870629501436937</v>
       </c>
       <c r="G92">
-        <v>-7.181449008827079</v>
+        <v>-5.883078730263803</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-7.237715828818376</v>
       </c>
       <c r="E93">
-        <v>-36.90239836327687</v>
+        <v>-32.70509447041829</v>
       </c>
       <c r="F93">
-        <v>7.751095768302676</v>
+        <v>9.586641961469988</v>
       </c>
       <c r="G93">
-        <v>-8.108207207663586</v>
+        <v>-5.823937533041313</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-6.759635224102191</v>
       </c>
       <c r="E94">
-        <v>-38.01174602740652</v>
+        <v>-34.82749136429445</v>
       </c>
       <c r="F94">
-        <v>7.360167653369117</v>
+        <v>9.765360571889177</v>
       </c>
       <c r="G94">
-        <v>-8.253457288362471</v>
+        <v>-5.435704147875221</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-6.271328970068963</v>
       </c>
       <c r="E95">
-        <v>-38.64528518931851</v>
+        <v>-37.75209556180089</v>
       </c>
       <c r="F95">
-        <v>7.156929367827064</v>
+        <v>9.859767948051431</v>
       </c>
       <c r="G95">
-        <v>-7.81894976069119</v>
+        <v>-5.503583507244167</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-5.788722225601097</v>
       </c>
       <c r="E96">
-        <v>-41.82156361008125</v>
+        <v>-38.72616897986956</v>
       </c>
       <c r="F96">
-        <v>7.057092871706861</v>
+        <v>9.998410143523179</v>
       </c>
       <c r="G96">
-        <v>-7.700270533068363</v>
+        <v>-5.366864034496746</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-5.316833431734066</v>
       </c>
       <c r="E97">
-        <v>-42.41500559325769</v>
+        <v>-42.12556414281907</v>
       </c>
       <c r="F97">
-        <v>6.698736163051379</v>
+        <v>9.357157683137636</v>
       </c>
       <c r="G97">
-        <v>-7.76440347394906</v>
+        <v>-5.31335943484647</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-4.878194369843349</v>
       </c>
       <c r="E98">
-        <v>-45.34991390806103</v>
+        <v>-44.55445141962228</v>
       </c>
       <c r="F98">
-        <v>6.492974670400399</v>
+        <v>9.398733443084144</v>
       </c>
       <c r="G98">
-        <v>-5.921339192246568</v>
+        <v>-5.832709634867454</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-4.480218645912658</v>
       </c>
       <c r="E99">
-        <v>-48.91080357846801</v>
+        <v>-46.24014541081254</v>
       </c>
       <c r="F99">
-        <v>6.326621928570201</v>
+        <v>9.338458117386841</v>
       </c>
       <c r="G99">
-        <v>-9.394804333493239</v>
+        <v>-5.376790085432158</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-4.141417508864325</v>
       </c>
       <c r="E100">
-        <v>-49.11279189634254</v>
+        <v>-48.3728827625847</v>
       </c>
       <c r="F100">
-        <v>6.439939275803563</v>
+        <v>8.847502981830434</v>
       </c>
       <c r="G100">
-        <v>-7.263408113775899</v>
+        <v>-5.147540602886501</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-3.874394929245178</v>
       </c>
       <c r="E101">
-        <v>-52.00227965379473</v>
+        <v>-51.07653819421593</v>
       </c>
       <c r="F101">
-        <v>6.185592378243586</v>
+        <v>8.642511870864057</v>
       </c>
       <c r="G101">
-        <v>-7.866635010647874</v>
+        <v>-4.939868924386395</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-3.68801666500365</v>
       </c>
       <c r="E102">
-        <v>-54.5691983898272</v>
+        <v>-52.43050169895533</v>
       </c>
       <c r="F102">
-        <v>5.079506519981518</v>
+        <v>8.537713454001087</v>
       </c>
       <c r="G102">
-        <v>-7.122033683422523</v>
+        <v>-5.364362941178459</v>
       </c>
     </row>
   </sheetData>
